--- a/Students Performance Analysis.xlsx
+++ b/Students Performance Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cb4cb213c5f970f8/Desktop/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="525" documentId="8_{5D16C158-3E5A-42E8-A608-CD86E5D033FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8C73B0-D84F-4260-8F36-FDC3C48966AD}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{3633BC59-2319-4548-968E-EA03AA3C3682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08590F82-3E8F-4806-BF6C-9BB1831ED712}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{13A90805-9504-4BFE-9056-C057E9428259}"/>
   </bookViews>
@@ -36,30 +36,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10052" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10054" uniqueCount="88">
   <si>
     <t>female</t>
   </si>
@@ -161,9 +139,6 @@
   </si>
   <si>
     <t xml:space="preserve">Master’s Degree  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associate Degree  </t>
   </si>
   <si>
     <t>Column1</t>
@@ -321,12 +296,18 @@
   <si>
     <t xml:space="preserve">eligible for bonus points. </t>
   </si>
+  <si>
+    <t xml:space="preserve">Associate's Degree  </t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -353,6 +334,12 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -450,7 +437,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -484,7 +471,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -529,6 +516,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B34FB7F7-A570-4255-8952-441488D33067}" name="Table1" displayName="Table1" ref="A2:H999" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A2:H999" xr:uid="{B34FB7F7-A570-4255-8952-441488D33067}"/>
@@ -558,20 +549,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DCFCF6C7-21E5-49D8-AE27-AC50F864E402}" name="Table5" displayName="Table5" ref="I7:L9" totalsRowShown="0" headerRowDxfId="10" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DCFCF6C7-21E5-49D8-AE27-AC50F864E402}" name="Table5" displayName="Table5" ref="I7:L9" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="I7:L9" xr:uid="{DCFCF6C7-21E5-49D8-AE27-AC50F864E402}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3058CE40-474A-4902-A4FD-928719D05B7F}" name="Test Preparation" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{CEB52EA9-2F88-4977-A470-C6EB3A5467AF}" name="Math" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{FAAE96F6-3269-468A-9178-258428C9E4E2}" name="Reading" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{13AAC915-9BA5-48F6-ACE7-9DFE4BE515B6}" name="Writing" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{3058CE40-474A-4902-A4FD-928719D05B7F}" name="Test Preparation" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{CEB52EA9-2F88-4977-A470-C6EB3A5467AF}" name="Math" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{FAAE96F6-3269-468A-9178-258428C9E4E2}" name="Reading" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{13AAC915-9BA5-48F6-ACE7-9DFE4BE515B6}" name="Writing" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{78B3ED36-FA33-4E51-B610-519D22A38F4A}" name="Table4" displayName="Table4" ref="C12:F16" totalsRowShown="0" headerRowDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{78B3ED36-FA33-4E51-B610-519D22A38F4A}" name="Table4" displayName="Table4" ref="C12:F16" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="C12:F16" xr:uid="{78B3ED36-FA33-4E51-B610-519D22A38F4A}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{EFDAD035-A3AB-4423-8DBC-78FAA5BC734A}" name="Column1"/>
@@ -1267,10 +1258,10 @@
         <v>44</v>
       </c>
       <c r="K13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" t="s">
         <v>35</v>
-      </c>
-      <c r="L13" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1335,8 +1326,7 @@
         <v>31</v>
       </c>
       <c r="L15">
-        <f>COUNTIF(C:C, "High School")</f>
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -1401,6 +1391,7 @@
         <v>33</v>
       </c>
       <c r="L17">
+        <f>COUNTIF(C:C,"master's degree")</f>
         <v>59</v>
       </c>
     </row>
@@ -1430,7 +1421,7 @@
         <v>43</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="L18">
         <v>222</v>
@@ -1462,7 +1453,7 @@
         <v>41</v>
       </c>
       <c r="K19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L19">
         <f>COUNTIF(C:C, "Some High School")</f>
@@ -1579,7 +1570,7 @@
         <v>60</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
@@ -1611,7 +1602,7 @@
         <v>46</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
@@ -1643,7 +1634,7 @@
         <v>38</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -1675,7 +1666,7 @@
         <v>43</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
@@ -1707,7 +1698,7 @@
         <v>50</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -26986,6 +26977,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="2">
@@ -27008,34 +27000,34 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="18" x14ac:dyDescent="0.35">
       <c r="B4" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="I7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="I8" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J8" s="4">
         <v>69</v>
@@ -27049,7 +27041,7 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="I9" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J9" s="4">
         <v>64</v>
@@ -27063,19 +27055,19 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="E12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="I12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
@@ -27083,26 +27075,26 @@
         <v>24</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="I13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="I14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="4">
         <v>68</v>
@@ -27114,7 +27106,7 @@
         <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
@@ -27133,115 +27125,115 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B26" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="3:15" x14ac:dyDescent="0.3">
@@ -27274,7 +27266,7 @@
         <v>23</v>
       </c>
       <c r="M53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="3:15" x14ac:dyDescent="0.3">
@@ -27543,7 +27535,7 @@
         <v>30</v>
       </c>
       <c r="M62" t="str">
-        <f>IF(F11&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M62:M93" si="1">IF(F11&gt;=69.75,"Bonus","No Bonus")</f>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27573,11 +27565,11 @@
         <v>44</v>
       </c>
       <c r="M63" t="str">
-        <f>IF(F12&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>Bonus</v>
       </c>
       <c r="O63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="3:15" x14ac:dyDescent="0.3">
@@ -27606,11 +27598,11 @@
         <v>47</v>
       </c>
       <c r="M64" t="str">
-        <f>IF(F13&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>Bonus</v>
       </c>
       <c r="O64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="4:15" x14ac:dyDescent="0.3">
@@ -27639,11 +27631,11 @@
         <v>44</v>
       </c>
       <c r="M65" t="str">
-        <f>IF(F14&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
       <c r="O65" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="4:15" x14ac:dyDescent="0.3">
@@ -27672,11 +27664,11 @@
         <v>33</v>
       </c>
       <c r="M66" t="str">
-        <f>IF(F15&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
       <c r="O66" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="4:15" x14ac:dyDescent="0.3">
@@ -27705,7 +27697,7 @@
         <v>38</v>
       </c>
       <c r="M67" t="str">
-        <f>IF(F16&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -27735,7 +27727,7 @@
         <v>43</v>
       </c>
       <c r="M68" t="str">
-        <f>IF(F17&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27765,7 +27757,7 @@
         <v>41</v>
       </c>
       <c r="M69" t="str">
-        <f>IF(F18&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27795,7 +27787,7 @@
         <v>39</v>
       </c>
       <c r="M70" t="str">
-        <f>IF(F19&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27825,7 +27817,7 @@
         <v>54</v>
       </c>
       <c r="M71" t="str">
-        <f>IF(F20&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27855,7 +27847,7 @@
         <v>43</v>
       </c>
       <c r="M72" t="str">
-        <f>IF(F21&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27885,7 +27877,7 @@
         <v>60</v>
       </c>
       <c r="M73" t="str">
-        <f>IF(F22&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27915,7 +27907,7 @@
         <v>46</v>
       </c>
       <c r="M74" t="str">
-        <f>IF(F23&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27945,7 +27937,7 @@
         <v>38</v>
       </c>
       <c r="M75" t="str">
-        <f>IF(F24&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -27975,7 +27967,7 @@
         <v>43</v>
       </c>
       <c r="M76" t="str">
-        <f>IF(F25&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28005,7 +27997,7 @@
         <v>50</v>
       </c>
       <c r="M77" t="str">
-        <f>IF(F26&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28035,7 +28027,7 @@
         <v>45</v>
       </c>
       <c r="M78" t="str">
-        <f>IF(F27&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28065,7 +28057,7 @@
         <v>57</v>
       </c>
       <c r="M79" t="str">
-        <f>IF(F28&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28095,7 +28087,7 @@
         <v>46</v>
       </c>
       <c r="M80" t="str">
-        <f>IF(F29&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28125,7 +28117,7 @@
         <v>50</v>
       </c>
       <c r="M81" t="str">
-        <f>IF(F30&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28155,7 +28147,7 @@
         <v>54</v>
       </c>
       <c r="M82" t="str">
-        <f>IF(F31&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28185,7 +28177,7 @@
         <v>51</v>
       </c>
       <c r="M83" t="str">
-        <f>IF(F32&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28215,7 +28207,7 @@
         <v>54</v>
       </c>
       <c r="M84" t="str">
-        <f>IF(F33&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28245,7 +28237,7 @@
         <v>64</v>
       </c>
       <c r="M85" t="str">
-        <f>IF(F34&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28275,7 +28267,7 @@
         <v>48</v>
       </c>
       <c r="M86" t="str">
-        <f>IF(F35&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28305,7 +28297,7 @@
         <v>51</v>
       </c>
       <c r="M87" t="str">
-        <f>IF(F36&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28335,7 +28327,7 @@
         <v>43</v>
       </c>
       <c r="M88" t="str">
-        <f>IF(F37&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28365,7 +28357,7 @@
         <v>40</v>
       </c>
       <c r="M89" t="str">
-        <f>IF(F38&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28395,7 +28387,7 @@
         <v>51</v>
       </c>
       <c r="M90" t="str">
-        <f>IF(F39&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28425,7 +28417,7 @@
         <v>60</v>
       </c>
       <c r="M91" t="str">
-        <f>IF(F40&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28455,7 +28447,7 @@
         <v>69</v>
       </c>
       <c r="M92" t="str">
-        <f>IF(F41&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28485,7 +28477,7 @@
         <v>58</v>
       </c>
       <c r="M93" t="str">
-        <f>IF(F42&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="1"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28515,7 +28507,7 @@
         <v>54</v>
       </c>
       <c r="M94" t="str">
-        <f>IF(F43&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M94:M112" si="2">IF(F43&gt;=69.75,"Bonus","No Bonus")</f>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28545,7 +28537,7 @@
         <v>54</v>
       </c>
       <c r="M95" t="str">
-        <f>IF(F44&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28575,7 +28567,7 @@
         <v>53</v>
       </c>
       <c r="M96" t="str">
-        <f>IF(F45&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28605,7 +28597,7 @@
         <v>61</v>
       </c>
       <c r="M97" t="str">
-        <f>IF(F46&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28635,7 +28627,7 @@
         <v>58</v>
       </c>
       <c r="M98" t="str">
-        <f>IF(F47&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28665,7 +28657,7 @@
         <v>58</v>
       </c>
       <c r="M99" t="str">
-        <f>IF(F48&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28695,7 +28687,7 @@
         <v>45</v>
       </c>
       <c r="M100" t="str">
-        <f>IF(F49&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28725,7 +28717,7 @@
         <v>51</v>
       </c>
       <c r="M101" t="str">
-        <f>IF(F50&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28755,7 +28747,7 @@
         <v>62</v>
       </c>
       <c r="M102" t="str">
-        <f>IF(F51&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28785,7 +28777,7 @@
         <v>55</v>
       </c>
       <c r="M103" t="str">
-        <f>IF(F52&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>No Bonus</v>
       </c>
     </row>
@@ -28815,7 +28807,7 @@
         <v>52</v>
       </c>
       <c r="M104" t="str">
-        <f>IF(F53&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -28845,7 +28837,7 @@
         <v>64</v>
       </c>
       <c r="M105" t="str">
-        <f>IF(F54&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -28875,7 +28867,7 @@
         <v>55</v>
       </c>
       <c r="M106" t="str">
-        <f>IF(F55&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -28905,7 +28897,7 @@
         <v>70</v>
       </c>
       <c r="M107" t="str">
-        <f>IF(F56&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -28935,7 +28927,7 @@
         <v>59</v>
       </c>
       <c r="M108" t="str">
-        <f>IF(F57&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -28965,7 +28957,7 @@
         <v>54</v>
       </c>
       <c r="M109" t="str">
-        <f>IF(F58&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -28995,7 +28987,7 @@
         <v>58</v>
       </c>
       <c r="M110" t="str">
-        <f>IF(F59&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29025,7 +29017,7 @@
         <v>55</v>
       </c>
       <c r="M111" t="str">
-        <f>IF(F60&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29055,7 +29047,7 @@
         <v>66</v>
       </c>
       <c r="M112" t="str">
-        <f>IF(F61&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" si="2"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29084,9 +29076,8 @@
       <c r="K113" s="1">
         <v>57</v>
       </c>
-      <c r="M113" t="e">
-        <f>IF(#REF!&gt;=69.75,"Bonus","No Bonus")</f>
-        <v>#REF!</v>
+      <c r="M113" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
@@ -29235,7 +29226,7 @@
         <v>66</v>
       </c>
       <c r="M118" t="str">
-        <f t="shared" ref="M118:M181" si="1">IF(F66&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M118:M181" si="3">IF(F66&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -29265,7 +29256,7 @@
         <v>58</v>
       </c>
       <c r="M119" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29295,7 +29286,7 @@
         <v>67</v>
       </c>
       <c r="M120" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29325,7 +29316,7 @@
         <v>65</v>
       </c>
       <c r="M121" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29355,7 +29346,7 @@
         <v>58</v>
       </c>
       <c r="M122" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29385,7 +29376,7 @@
         <v>60</v>
       </c>
       <c r="M123" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29415,7 +29406,7 @@
         <v>52</v>
       </c>
       <c r="M124" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29445,7 +29436,7 @@
         <v>51</v>
       </c>
       <c r="M125" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29475,7 +29466,7 @@
         <v>54</v>
       </c>
       <c r="M126" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29505,7 +29496,7 @@
         <v>53</v>
       </c>
       <c r="M127" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29535,7 +29526,7 @@
         <v>55</v>
       </c>
       <c r="M128" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29565,7 +29556,7 @@
         <v>54</v>
       </c>
       <c r="M129" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29595,7 +29586,7 @@
         <v>55</v>
       </c>
       <c r="M130" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29625,7 +29616,7 @@
         <v>53</v>
       </c>
       <c r="M131" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29655,7 +29646,7 @@
         <v>56</v>
       </c>
       <c r="M132" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29685,7 +29676,7 @@
         <v>52</v>
       </c>
       <c r="M133" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29715,7 +29706,7 @@
         <v>60</v>
       </c>
       <c r="M134" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29745,7 +29736,7 @@
         <v>61</v>
       </c>
       <c r="M135" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29775,7 +29766,7 @@
         <v>58</v>
       </c>
       <c r="M136" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29805,7 +29796,7 @@
         <v>73</v>
       </c>
       <c r="M137" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29835,7 +29826,7 @@
         <v>63</v>
       </c>
       <c r="M138" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29865,7 +29856,7 @@
         <v>55</v>
       </c>
       <c r="M139" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29895,7 +29886,7 @@
         <v>66</v>
       </c>
       <c r="M140" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29925,7 +29916,7 @@
         <v>64</v>
       </c>
       <c r="M141" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29955,7 +29946,7 @@
         <v>60</v>
       </c>
       <c r="M142" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -29985,7 +29976,7 @@
         <v>59</v>
       </c>
       <c r="M143" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30015,7 +30006,7 @@
         <v>59</v>
       </c>
       <c r="M144" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30045,7 +30036,7 @@
         <v>54</v>
       </c>
       <c r="M145" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30075,7 +30066,7 @@
         <v>47</v>
       </c>
       <c r="M146" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30105,7 +30096,7 @@
         <v>51</v>
       </c>
       <c r="M147" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30135,7 +30126,7 @@
         <v>79</v>
       </c>
       <c r="M148" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30165,7 +30156,7 @@
         <v>54</v>
       </c>
       <c r="M149" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30195,7 +30186,7 @@
         <v>61</v>
       </c>
       <c r="M150" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30225,7 +30216,7 @@
         <v>62</v>
       </c>
       <c r="M151" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30255,7 +30246,7 @@
         <v>54</v>
       </c>
       <c r="M152" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30285,7 +30276,7 @@
         <v>70</v>
       </c>
       <c r="M153" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30315,7 +30306,7 @@
         <v>62</v>
       </c>
       <c r="M154" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30345,7 +30336,7 @@
         <v>73</v>
       </c>
       <c r="M155" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30375,7 +30366,7 @@
         <v>69</v>
       </c>
       <c r="M156" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30405,7 +30396,7 @@
         <v>72</v>
       </c>
       <c r="M157" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30435,7 +30426,7 @@
         <v>58</v>
       </c>
       <c r="M158" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30465,7 +30456,7 @@
         <v>62</v>
       </c>
       <c r="M159" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30495,7 +30486,7 @@
         <v>61</v>
       </c>
       <c r="M160" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30525,7 +30516,7 @@
         <v>57</v>
       </c>
       <c r="M161" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30555,7 +30546,7 @@
         <v>66</v>
       </c>
       <c r="M162" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30585,7 +30576,7 @@
         <v>56</v>
       </c>
       <c r="M163" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30615,7 +30606,7 @@
         <v>56</v>
       </c>
       <c r="M164" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30645,7 +30636,7 @@
         <v>65</v>
       </c>
       <c r="M165" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30675,7 +30666,7 @@
         <v>60</v>
       </c>
       <c r="M166" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30705,7 +30696,7 @@
         <v>65</v>
       </c>
       <c r="M167" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30735,7 +30726,7 @@
         <v>67</v>
       </c>
       <c r="M168" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30765,7 +30756,7 @@
         <v>70</v>
       </c>
       <c r="M169" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30795,7 +30786,7 @@
         <v>73</v>
       </c>
       <c r="M170" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30825,7 +30816,7 @@
         <v>62</v>
       </c>
       <c r="M171" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30855,7 +30846,7 @@
         <v>56</v>
       </c>
       <c r="M172" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30885,7 +30876,7 @@
         <v>64</v>
       </c>
       <c r="M173" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30915,7 +30906,7 @@
         <v>53</v>
       </c>
       <c r="M174" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30945,7 +30936,7 @@
         <v>68</v>
       </c>
       <c r="M175" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -30975,7 +30966,7 @@
         <v>57</v>
       </c>
       <c r="M176" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31005,7 +30996,7 @@
         <v>67</v>
       </c>
       <c r="M177" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31035,7 +31026,7 @@
         <v>68</v>
       </c>
       <c r="M178" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31065,7 +31056,7 @@
         <v>62</v>
       </c>
       <c r="M179" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31095,7 +31086,7 @@
         <v>65</v>
       </c>
       <c r="M180" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31125,7 +31116,7 @@
         <v>61</v>
       </c>
       <c r="M181" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31155,7 +31146,7 @@
         <v>62</v>
       </c>
       <c r="M182" t="str">
-        <f t="shared" ref="M182:M245" si="2">IF(F130&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M182:M245" si="4">IF(F130&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -31185,7 +31176,7 @@
         <v>52</v>
       </c>
       <c r="M183" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31215,7 +31206,7 @@
         <v>65</v>
       </c>
       <c r="M184" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31245,7 +31236,7 @@
         <v>67</v>
       </c>
       <c r="M185" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31275,7 +31266,7 @@
         <v>58</v>
       </c>
       <c r="M186" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31305,7 +31296,7 @@
         <v>63</v>
       </c>
       <c r="M187" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31335,7 +31326,7 @@
         <v>62</v>
       </c>
       <c r="M188" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31365,7 +31356,7 @@
         <v>73</v>
       </c>
       <c r="M189" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31395,7 +31386,7 @@
         <v>65</v>
       </c>
       <c r="M190" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31425,7 +31416,7 @@
         <v>62</v>
       </c>
       <c r="M191" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31455,7 +31446,7 @@
         <v>79</v>
       </c>
       <c r="M192" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31485,7 +31476,7 @@
         <v>70</v>
       </c>
       <c r="M193" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31515,7 +31506,7 @@
         <v>69</v>
       </c>
       <c r="M194" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31545,7 +31536,7 @@
         <v>76</v>
       </c>
       <c r="M195" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31575,7 +31566,7 @@
         <v>64</v>
       </c>
       <c r="M196" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31605,7 +31596,7 @@
         <v>72</v>
       </c>
       <c r="M197" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31635,7 +31626,7 @@
         <v>70</v>
       </c>
       <c r="M198" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31665,7 +31656,7 @@
         <v>74</v>
       </c>
       <c r="M199" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31695,7 +31686,7 @@
         <v>55</v>
       </c>
       <c r="M200" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31725,7 +31716,7 @@
         <v>63</v>
       </c>
       <c r="M201" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31755,7 +31746,7 @@
         <v>65</v>
       </c>
       <c r="M202" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31785,7 +31776,7 @@
         <v>68</v>
       </c>
       <c r="M203" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31815,7 +31806,7 @@
         <v>72</v>
       </c>
       <c r="M204" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31845,7 +31836,7 @@
         <v>67</v>
       </c>
       <c r="M205" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31875,7 +31866,7 @@
         <v>80</v>
       </c>
       <c r="M206" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31905,7 +31896,7 @@
         <v>76</v>
       </c>
       <c r="M207" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31935,7 +31926,7 @@
         <v>64</v>
       </c>
       <c r="M208" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31965,7 +31956,7 @@
         <v>79</v>
       </c>
       <c r="M209" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -31995,7 +31986,7 @@
         <v>73</v>
       </c>
       <c r="M210" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32025,7 +32016,7 @@
         <v>57</v>
       </c>
       <c r="M211" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32055,7 +32046,7 @@
         <v>73</v>
       </c>
       <c r="M212" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32085,7 +32076,7 @@
         <v>67</v>
       </c>
       <c r="M213" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32115,7 +32106,7 @@
         <v>78</v>
       </c>
       <c r="M214" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32145,7 +32136,7 @@
         <v>66</v>
       </c>
       <c r="M215" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32175,7 +32166,7 @@
         <v>68</v>
       </c>
       <c r="M216" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32205,7 +32196,7 @@
         <v>59</v>
       </c>
       <c r="M217" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32235,7 +32226,7 @@
         <v>65</v>
       </c>
       <c r="M218" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32265,7 +32256,7 @@
         <v>61</v>
       </c>
       <c r="M219" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32295,7 +32286,7 @@
         <v>68</v>
       </c>
       <c r="M220" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32325,7 +32316,7 @@
         <v>72</v>
       </c>
       <c r="M221" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32355,7 +32346,7 @@
         <v>66</v>
       </c>
       <c r="M222" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32385,7 +32376,7 @@
         <v>77</v>
       </c>
       <c r="M223" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32415,7 +32406,7 @@
         <v>73</v>
       </c>
       <c r="M224" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32445,7 +32436,7 @@
         <v>62</v>
       </c>
       <c r="M225" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32475,7 +32466,7 @@
         <v>80</v>
       </c>
       <c r="M226" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32505,7 +32496,7 @@
         <v>69</v>
       </c>
       <c r="M227" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32535,7 +32526,7 @@
         <v>70</v>
       </c>
       <c r="M228" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32565,7 +32556,7 @@
         <v>66</v>
       </c>
       <c r="M229" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32595,7 +32586,7 @@
         <v>64</v>
       </c>
       <c r="M230" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32625,7 +32616,7 @@
         <v>67</v>
       </c>
       <c r="M231" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32655,7 +32646,7 @@
         <v>64</v>
       </c>
       <c r="M232" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32685,7 +32676,7 @@
         <v>75</v>
       </c>
       <c r="M233" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32715,7 +32706,7 @@
         <v>70</v>
       </c>
       <c r="M234" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32745,7 +32736,7 @@
         <v>67</v>
       </c>
       <c r="M235" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32775,7 +32766,7 @@
         <v>72</v>
       </c>
       <c r="M236" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32805,7 +32796,7 @@
         <v>68</v>
       </c>
       <c r="M237" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32835,7 +32826,7 @@
         <v>65</v>
       </c>
       <c r="M238" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32865,7 +32856,7 @@
         <v>59</v>
       </c>
       <c r="M239" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32895,7 +32886,7 @@
         <v>73</v>
       </c>
       <c r="M240" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32925,7 +32916,7 @@
         <v>61</v>
       </c>
       <c r="M241" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32955,7 +32946,7 @@
         <v>76</v>
       </c>
       <c r="M242" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -32985,7 +32976,7 @@
         <v>65</v>
       </c>
       <c r="M243" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33015,7 +33006,7 @@
         <v>80</v>
       </c>
       <c r="M244" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33045,7 +33036,7 @@
         <v>75</v>
       </c>
       <c r="M245" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33075,7 +33066,7 @@
         <v>69</v>
       </c>
       <c r="M246" t="str">
-        <f t="shared" ref="M246:M309" si="3">IF(F194&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M246:M309" si="5">IF(F194&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -33105,7 +33096,7 @@
         <v>70</v>
       </c>
       <c r="M247" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33135,7 +33126,7 @@
         <v>74</v>
       </c>
       <c r="M248" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33165,7 +33156,7 @@
         <v>68</v>
       </c>
       <c r="M249" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33195,7 +33186,7 @@
         <v>74</v>
       </c>
       <c r="M250" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33225,7 +33216,7 @@
         <v>74</v>
       </c>
       <c r="M251" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33255,7 +33246,7 @@
         <v>72</v>
       </c>
       <c r="M252" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33285,7 +33276,7 @@
         <v>74</v>
       </c>
       <c r="M253" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33315,7 +33306,7 @@
         <v>70</v>
       </c>
       <c r="M254" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33345,7 +33336,7 @@
         <v>57</v>
       </c>
       <c r="M255" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33375,7 +33366,7 @@
         <v>63</v>
       </c>
       <c r="M256" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33405,7 +33396,7 @@
         <v>87</v>
       </c>
       <c r="M257" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33435,7 +33426,7 @@
         <v>66</v>
       </c>
       <c r="M258" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33465,7 +33456,7 @@
         <v>70</v>
       </c>
       <c r="M259" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33495,7 +33486,7 @@
         <v>63</v>
       </c>
       <c r="M260" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33525,7 +33516,7 @@
         <v>70</v>
       </c>
       <c r="M261" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33555,7 +33546,7 @@
         <v>72</v>
       </c>
       <c r="M262" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33585,7 +33576,7 @@
         <v>78</v>
       </c>
       <c r="M263" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33615,7 +33606,7 @@
         <v>62</v>
       </c>
       <c r="M264" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33645,7 +33636,7 @@
         <v>62</v>
       </c>
       <c r="M265" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33675,7 +33666,7 @@
         <v>66</v>
       </c>
       <c r="M266" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33705,7 +33696,7 @@
         <v>67</v>
       </c>
       <c r="M267" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33735,7 +33726,7 @@
         <v>63</v>
       </c>
       <c r="M268" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33765,7 +33756,7 @@
         <v>62</v>
       </c>
       <c r="M269" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33795,7 +33786,7 @@
         <v>70</v>
       </c>
       <c r="M270" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33825,7 +33816,7 @@
         <v>64</v>
       </c>
       <c r="M271" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33855,7 +33846,7 @@
         <v>70</v>
       </c>
       <c r="M272" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33885,7 +33876,7 @@
         <v>79</v>
       </c>
       <c r="M273" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33915,7 +33906,7 @@
         <v>80</v>
       </c>
       <c r="M274" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33945,7 +33936,7 @@
         <v>69</v>
       </c>
       <c r="M275" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -33975,7 +33966,7 @@
         <v>75</v>
       </c>
       <c r="M276" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34005,7 +33996,7 @@
         <v>64</v>
       </c>
       <c r="M277" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34035,7 +34026,7 @@
         <v>72</v>
       </c>
       <c r="M278" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34065,7 +34056,7 @@
         <v>74</v>
       </c>
       <c r="M279" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34095,7 +34086,7 @@
         <v>68</v>
       </c>
       <c r="M280" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34125,7 +34116,7 @@
         <v>70</v>
       </c>
       <c r="M281" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34155,7 +34146,7 @@
         <v>61</v>
       </c>
       <c r="M282" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34185,7 +34176,7 @@
         <v>79</v>
       </c>
       <c r="M283" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34215,7 +34206,7 @@
         <v>70</v>
       </c>
       <c r="M284" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34245,7 +34236,7 @@
         <v>81</v>
       </c>
       <c r="M285" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34275,7 +34266,7 @@
         <v>80</v>
       </c>
       <c r="M286" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34305,7 +34296,7 @@
         <v>68</v>
       </c>
       <c r="M287" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34335,7 +34326,7 @@
         <v>74</v>
       </c>
       <c r="M288" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34365,7 +34356,7 @@
         <v>74</v>
       </c>
       <c r="M289" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34395,7 +34386,7 @@
         <v>71</v>
       </c>
       <c r="M290" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34425,7 +34416,7 @@
         <v>80</v>
       </c>
       <c r="M291" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34455,7 +34446,7 @@
         <v>78</v>
       </c>
       <c r="M292" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34485,7 +34476,7 @@
         <v>67</v>
       </c>
       <c r="M293" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34515,7 +34506,7 @@
         <v>70</v>
       </c>
       <c r="M294" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34545,7 +34536,7 @@
         <v>71</v>
       </c>
       <c r="M295" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34575,7 +34566,7 @@
         <v>68</v>
       </c>
       <c r="M296" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34605,7 +34596,7 @@
         <v>77</v>
       </c>
       <c r="M297" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34635,7 +34626,7 @@
         <v>85</v>
       </c>
       <c r="M298" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34665,7 +34656,7 @@
         <v>70</v>
       </c>
       <c r="M299" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34695,7 +34686,7 @@
         <v>77</v>
       </c>
       <c r="M300" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34725,7 +34716,7 @@
         <v>74</v>
       </c>
       <c r="M301" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34755,7 +34746,7 @@
         <v>66</v>
       </c>
       <c r="M302" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34785,7 +34776,7 @@
         <v>75</v>
       </c>
       <c r="M303" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34815,7 +34806,7 @@
         <v>74</v>
       </c>
       <c r="M304" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34845,7 +34836,7 @@
         <v>70</v>
       </c>
       <c r="M305" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34875,7 +34866,7 @@
         <v>68</v>
       </c>
       <c r="M306" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34905,7 +34896,7 @@
         <v>76</v>
       </c>
       <c r="M307" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34935,7 +34926,7 @@
         <v>74</v>
       </c>
       <c r="M308" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34965,7 +34956,7 @@
         <v>73</v>
       </c>
       <c r="M309" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -34995,7 +34986,7 @@
         <v>70</v>
       </c>
       <c r="M310" t="str">
-        <f t="shared" ref="M310:M373" si="4">IF(F258&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M310:M373" si="6">IF(F258&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -35025,7 +35016,7 @@
         <v>62</v>
       </c>
       <c r="M311" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35055,7 +35046,7 @@
         <v>81</v>
       </c>
       <c r="M312" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35085,7 +35076,7 @@
         <v>78</v>
       </c>
       <c r="M313" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35115,7 +35106,7 @@
         <v>74</v>
       </c>
       <c r="M314" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35145,7 +35136,7 @@
         <v>81</v>
       </c>
       <c r="M315" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35175,7 +35166,7 @@
         <v>80</v>
       </c>
       <c r="M316" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35205,7 +35196,7 @@
         <v>77</v>
       </c>
       <c r="M317" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35235,7 +35226,7 @@
         <v>74</v>
       </c>
       <c r="M318" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35265,7 +35256,7 @@
         <v>76</v>
       </c>
       <c r="M319" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35295,7 +35286,7 @@
         <v>74</v>
       </c>
       <c r="M320" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35325,7 +35316,7 @@
         <v>67</v>
       </c>
       <c r="M321" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35355,7 +35346,7 @@
         <v>84</v>
       </c>
       <c r="M322" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35385,7 +35376,7 @@
         <v>76</v>
       </c>
       <c r="M323" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35415,7 +35406,7 @@
         <v>81</v>
       </c>
       <c r="M324" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35445,7 +35436,7 @@
         <v>75</v>
       </c>
       <c r="M325" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35475,7 +35466,7 @@
         <v>62</v>
       </c>
       <c r="M326" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35505,7 +35496,7 @@
         <v>70</v>
       </c>
       <c r="M327" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35535,7 +35526,7 @@
         <v>77</v>
       </c>
       <c r="M328" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35565,7 +35556,7 @@
         <v>71</v>
       </c>
       <c r="M329" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35595,7 +35586,7 @@
         <v>81</v>
       </c>
       <c r="M330" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35625,7 +35616,7 @@
         <v>82</v>
       </c>
       <c r="M331" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35655,7 +35646,7 @@
         <v>71</v>
       </c>
       <c r="M332" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35685,7 +35676,7 @@
         <v>75</v>
       </c>
       <c r="M333" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35715,7 +35706,7 @@
         <v>77</v>
       </c>
       <c r="M334" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35745,7 +35736,7 @@
         <v>68</v>
       </c>
       <c r="M335" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35775,7 +35766,7 @@
         <v>81</v>
       </c>
       <c r="M336" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35805,7 +35796,7 @@
         <v>70</v>
       </c>
       <c r="M337" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35835,7 +35826,7 @@
         <v>76</v>
       </c>
       <c r="M338" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35865,7 +35856,7 @@
         <v>83</v>
       </c>
       <c r="M339" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35895,7 +35886,7 @@
         <v>68</v>
       </c>
       <c r="M340" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35925,7 +35916,7 @@
         <v>81</v>
       </c>
       <c r="M341" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35955,7 +35946,7 @@
         <v>73</v>
       </c>
       <c r="M342" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -35985,7 +35976,7 @@
         <v>78</v>
       </c>
       <c r="M343" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36015,7 +36006,7 @@
         <v>78</v>
       </c>
       <c r="M344" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36045,7 +36036,7 @@
         <v>69</v>
       </c>
       <c r="M345" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36075,7 +36066,7 @@
         <v>73</v>
       </c>
       <c r="M346" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36105,7 +36096,7 @@
         <v>83</v>
       </c>
       <c r="M347" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36135,7 +36126,7 @@
         <v>82</v>
       </c>
       <c r="M348" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36165,7 +36156,7 @@
         <v>79</v>
       </c>
       <c r="M349" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36195,7 +36186,7 @@
         <v>81</v>
       </c>
       <c r="M350" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36225,7 +36216,7 @@
         <v>75</v>
       </c>
       <c r="M351" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36255,7 +36246,7 @@
         <v>70</v>
       </c>
       <c r="M352" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36285,7 +36276,7 @@
         <v>86</v>
       </c>
       <c r="M353" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36315,7 +36306,7 @@
         <v>81</v>
       </c>
       <c r="M354" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36345,7 +36336,7 @@
         <v>84</v>
       </c>
       <c r="M355" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36375,7 +36366,7 @@
         <v>79</v>
       </c>
       <c r="M356" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36405,7 +36396,7 @@
         <v>77</v>
       </c>
       <c r="M357" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36435,7 +36426,7 @@
         <v>72</v>
       </c>
       <c r="M358" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36465,7 +36456,7 @@
         <v>74</v>
       </c>
       <c r="M359" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36495,7 +36486,7 @@
         <v>84</v>
       </c>
       <c r="M360" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36525,7 +36516,7 @@
         <v>83</v>
       </c>
       <c r="M361" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36555,7 +36546,7 @@
         <v>75</v>
       </c>
       <c r="M362" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36585,7 +36576,7 @@
         <v>76</v>
       </c>
       <c r="M363" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36615,7 +36606,7 @@
         <v>78</v>
       </c>
       <c r="M364" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36645,7 +36636,7 @@
         <v>80</v>
       </c>
       <c r="M365" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36675,7 +36666,7 @@
         <v>69</v>
       </c>
       <c r="M366" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36705,7 +36696,7 @@
         <v>84</v>
       </c>
       <c r="M367" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36735,7 +36726,7 @@
         <v>73</v>
       </c>
       <c r="M368" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36765,7 +36756,7 @@
         <v>81</v>
       </c>
       <c r="M369" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36795,7 +36786,7 @@
         <v>75</v>
       </c>
       <c r="M370" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36825,7 +36816,7 @@
         <v>77</v>
       </c>
       <c r="M371" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36855,7 +36846,7 @@
         <v>66</v>
       </c>
       <c r="M372" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36885,7 +36876,7 @@
         <v>67</v>
       </c>
       <c r="M373" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36915,7 +36906,7 @@
         <v>82</v>
       </c>
       <c r="M374" t="str">
-        <f t="shared" ref="M374:M437" si="5">IF(F322&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M374:M437" si="7">IF(F322&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -36945,7 +36936,7 @@
         <v>74</v>
       </c>
       <c r="M375" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -36975,7 +36966,7 @@
         <v>88</v>
       </c>
       <c r="M376" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37005,7 +36996,7 @@
         <v>78</v>
       </c>
       <c r="M377" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37035,7 +37026,7 @@
         <v>73</v>
       </c>
       <c r="M378" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37065,7 +37056,7 @@
         <v>71</v>
       </c>
       <c r="M379" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37095,7 +37086,7 @@
         <v>85</v>
       </c>
       <c r="M380" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37125,7 +37116,7 @@
         <v>76</v>
       </c>
       <c r="M381" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37155,7 +37146,7 @@
         <v>74</v>
       </c>
       <c r="M382" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37185,7 +37176,7 @@
         <v>77</v>
       </c>
       <c r="M383" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37215,7 +37206,7 @@
         <v>77</v>
       </c>
       <c r="M384" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37245,7 +37236,7 @@
         <v>73</v>
       </c>
       <c r="M385" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37275,7 +37266,7 @@
         <v>81</v>
       </c>
       <c r="M386" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37305,7 +37296,7 @@
         <v>78</v>
       </c>
       <c r="M387" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37335,7 +37326,7 @@
         <v>81</v>
       </c>
       <c r="M388" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37365,7 +37356,7 @@
         <v>74</v>
       </c>
       <c r="M389" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37395,7 +37386,7 @@
         <v>72</v>
       </c>
       <c r="M390" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37425,7 +37416,7 @@
         <v>78</v>
       </c>
       <c r="M391" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37455,7 +37446,7 @@
         <v>88</v>
       </c>
       <c r="M392" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37485,7 +37476,7 @@
         <v>76</v>
       </c>
       <c r="M393" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37515,7 +37506,7 @@
         <v>76</v>
       </c>
       <c r="M394" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37545,7 +37536,7 @@
         <v>78</v>
       </c>
       <c r="M395" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37575,7 +37566,7 @@
         <v>74</v>
       </c>
       <c r="M396" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37605,7 +37596,7 @@
         <v>81</v>
       </c>
       <c r="M397" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37635,7 +37626,7 @@
         <v>77</v>
       </c>
       <c r="M398" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37665,7 +37656,7 @@
         <v>78</v>
       </c>
       <c r="M399" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37695,7 +37686,7 @@
         <v>82</v>
       </c>
       <c r="M400" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37725,7 +37716,7 @@
         <v>87</v>
       </c>
       <c r="M401" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37755,7 +37746,7 @@
         <v>77</v>
       </c>
       <c r="M402" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37785,7 +37776,7 @@
         <v>80</v>
       </c>
       <c r="M403" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37815,7 +37806,7 @@
         <v>80</v>
       </c>
       <c r="M404" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37845,7 +37836,7 @@
         <v>74</v>
       </c>
       <c r="M405" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37875,7 +37866,7 @@
         <v>83</v>
       </c>
       <c r="M406" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37905,7 +37896,7 @@
         <v>83</v>
       </c>
       <c r="M407" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37935,7 +37926,7 @@
         <v>70</v>
       </c>
       <c r="M408" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37965,7 +37956,7 @@
         <v>76</v>
       </c>
       <c r="M409" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -37995,7 +37986,7 @@
         <v>70</v>
       </c>
       <c r="M410" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38025,7 +38016,7 @@
         <v>82</v>
       </c>
       <c r="M411" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38055,7 +38046,7 @@
         <v>74</v>
       </c>
       <c r="M412" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38085,7 +38076,7 @@
         <v>79</v>
       </c>
       <c r="M413" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38115,7 +38106,7 @@
         <v>71</v>
       </c>
       <c r="M414" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38145,7 +38136,7 @@
         <v>75</v>
       </c>
       <c r="M415" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38175,7 +38166,7 @@
         <v>83</v>
       </c>
       <c r="M416" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38205,7 +38196,7 @@
         <v>77</v>
       </c>
       <c r="M417" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38235,7 +38226,7 @@
         <v>80</v>
       </c>
       <c r="M418" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38265,7 +38256,7 @@
         <v>76</v>
       </c>
       <c r="M419" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38295,7 +38286,7 @@
         <v>79</v>
       </c>
       <c r="M420" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38325,7 +38316,7 @@
         <v>82</v>
       </c>
       <c r="M421" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38355,7 +38346,7 @@
         <v>78</v>
       </c>
       <c r="M422" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38385,7 +38376,7 @@
         <v>74</v>
       </c>
       <c r="M423" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38415,7 +38406,7 @@
         <v>82</v>
       </c>
       <c r="M424" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38445,7 +38436,7 @@
         <v>84</v>
       </c>
       <c r="M425" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38475,7 +38466,7 @@
         <v>85</v>
       </c>
       <c r="M426" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38505,7 +38496,7 @@
         <v>80</v>
       </c>
       <c r="M427" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38535,7 +38526,7 @@
         <v>84</v>
       </c>
       <c r="M428" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38565,7 +38556,7 @@
         <v>76</v>
       </c>
       <c r="M429" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38595,7 +38586,7 @@
         <v>78</v>
       </c>
       <c r="M430" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38625,7 +38616,7 @@
         <v>76</v>
       </c>
       <c r="M431" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38655,7 +38646,7 @@
         <v>88</v>
       </c>
       <c r="M432" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38685,7 +38676,7 @@
         <v>72</v>
       </c>
       <c r="M433" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38715,7 +38706,7 @@
         <v>83</v>
       </c>
       <c r="M434" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38745,7 +38736,7 @@
         <v>89</v>
       </c>
       <c r="M435" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38775,7 +38766,7 @@
         <v>82</v>
       </c>
       <c r="M436" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38805,7 +38796,7 @@
         <v>83</v>
       </c>
       <c r="M437" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38835,7 +38826,7 @@
         <v>82</v>
       </c>
       <c r="M438" t="str">
-        <f t="shared" ref="M438:M501" si="6">IF(F386&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M438:M501" si="8">IF(F386&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -38865,7 +38856,7 @@
         <v>84</v>
       </c>
       <c r="M439" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38895,7 +38886,7 @@
         <v>79</v>
       </c>
       <c r="M440" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38925,7 +38916,7 @@
         <v>90</v>
       </c>
       <c r="M441" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38955,7 +38946,7 @@
         <v>71</v>
       </c>
       <c r="M442" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -38985,7 +38976,7 @@
         <v>73</v>
       </c>
       <c r="M443" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39015,7 +39006,7 @@
         <v>80</v>
       </c>
       <c r="M444" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39045,7 +39036,7 @@
         <v>72</v>
       </c>
       <c r="M445" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39075,7 +39066,7 @@
         <v>79</v>
       </c>
       <c r="M446" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39105,7 +39096,7 @@
         <v>82</v>
       </c>
       <c r="M447" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39135,7 +39126,7 @@
         <v>80</v>
       </c>
       <c r="M448" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39165,7 +39156,7 @@
         <v>84</v>
       </c>
       <c r="M449" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39195,7 +39186,7 @@
         <v>85</v>
       </c>
       <c r="M450" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39225,7 +39216,7 @@
         <v>90</v>
       </c>
       <c r="M451" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39255,7 +39246,7 @@
         <v>88</v>
       </c>
       <c r="M452" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39285,7 +39276,7 @@
         <v>83</v>
       </c>
       <c r="M453" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39315,7 +39306,7 @@
         <v>85</v>
       </c>
       <c r="M454" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39345,7 +39336,7 @@
         <v>79</v>
       </c>
       <c r="M455" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39375,7 +39366,7 @@
         <v>87</v>
       </c>
       <c r="M456" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39405,7 +39396,7 @@
         <v>82</v>
       </c>
       <c r="M457" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39435,7 +39426,7 @@
         <v>88</v>
       </c>
       <c r="M458" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39465,7 +39456,7 @@
         <v>85</v>
       </c>
       <c r="M459" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39495,7 +39486,7 @@
         <v>74</v>
       </c>
       <c r="M460" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39525,7 +39516,7 @@
         <v>71</v>
       </c>
       <c r="M461" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39555,7 +39546,7 @@
         <v>73</v>
       </c>
       <c r="M462" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39585,7 +39576,7 @@
         <v>80</v>
       </c>
       <c r="M463" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39615,7 +39606,7 @@
         <v>85</v>
       </c>
       <c r="M464" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39645,7 +39636,7 @@
         <v>94</v>
       </c>
       <c r="M465" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39675,7 +39666,7 @@
         <v>87</v>
       </c>
       <c r="M466" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39705,7 +39696,7 @@
         <v>84</v>
       </c>
       <c r="M467" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39735,7 +39726,7 @@
         <v>89</v>
       </c>
       <c r="M468" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39765,7 +39756,7 @@
         <v>87</v>
       </c>
       <c r="M469" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39795,7 +39786,7 @@
         <v>95</v>
       </c>
       <c r="M470" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39825,7 +39816,7 @@
         <v>91</v>
       </c>
       <c r="M471" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39855,7 +39846,7 @@
         <v>85</v>
       </c>
       <c r="M472" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39885,7 +39876,7 @@
         <v>88</v>
       </c>
       <c r="M473" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39915,7 +39906,7 @@
         <v>98</v>
       </c>
       <c r="M474" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39945,7 +39936,7 @@
         <v>91</v>
       </c>
       <c r="M475" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -39975,7 +39966,7 @@
         <v>77</v>
       </c>
       <c r="M476" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40005,7 +39996,7 @@
         <v>73</v>
       </c>
       <c r="M477" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40035,7 +40026,7 @@
         <v>86</v>
       </c>
       <c r="M478" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40065,7 +40056,7 @@
         <v>80</v>
       </c>
       <c r="M479" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40095,7 +40086,7 @@
         <v>91</v>
       </c>
       <c r="M480" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40125,7 +40116,7 @@
         <v>76</v>
       </c>
       <c r="M481" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40155,7 +40146,7 @@
         <v>79</v>
       </c>
       <c r="M482" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40185,7 +40176,7 @@
         <v>80</v>
       </c>
       <c r="M483" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40215,7 +40206,7 @@
         <v>93</v>
       </c>
       <c r="M484" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40245,7 +40236,7 @@
         <v>96</v>
       </c>
       <c r="M485" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40275,7 +40266,7 @@
         <v>92</v>
       </c>
       <c r="M486" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40305,7 +40296,7 @@
         <v>89</v>
       </c>
       <c r="M487" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40335,7 +40326,7 @@
         <v>81</v>
       </c>
       <c r="M488" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40365,7 +40356,7 @@
         <v>89</v>
       </c>
       <c r="M489" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40395,7 +40386,7 @@
         <v>86</v>
       </c>
       <c r="M490" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40425,7 +40416,7 @@
         <v>91</v>
       </c>
       <c r="M491" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40455,7 +40446,7 @@
         <v>94</v>
       </c>
       <c r="M492" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40485,7 +40476,7 @@
         <v>82</v>
       </c>
       <c r="M493" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40515,7 +40506,7 @@
         <v>83</v>
       </c>
       <c r="M494" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40545,7 +40536,7 @@
         <v>89</v>
       </c>
       <c r="M495" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40575,7 +40566,7 @@
         <v>82</v>
       </c>
       <c r="M496" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40605,7 +40596,7 @@
         <v>88</v>
       </c>
       <c r="M497" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40635,7 +40626,7 @@
         <v>83</v>
       </c>
       <c r="M498" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40665,7 +40656,7 @@
         <v>85</v>
       </c>
       <c r="M499" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40695,7 +40686,7 @@
         <v>89</v>
       </c>
       <c r="M500" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40725,7 +40716,7 @@
         <v>87</v>
       </c>
       <c r="M501" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40755,7 +40746,7 @@
         <v>90</v>
       </c>
       <c r="M502" t="str">
-        <f t="shared" ref="M502:M565" si="7">IF(F450&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M502:M565" si="9">IF(F450&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -40785,7 +40776,7 @@
         <v>79</v>
       </c>
       <c r="M503" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40815,7 +40806,7 @@
         <v>82</v>
       </c>
       <c r="M504" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40845,7 +40836,7 @@
         <v>96</v>
       </c>
       <c r="M505" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40875,7 +40866,7 @@
         <v>91</v>
       </c>
       <c r="M506" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40905,7 +40896,7 @@
         <v>87</v>
       </c>
       <c r="M507" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40935,7 +40926,7 @@
         <v>93</v>
       </c>
       <c r="M508" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40965,7 +40956,7 @@
         <v>77</v>
       </c>
       <c r="M509" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -40995,7 +40986,7 @@
         <v>80</v>
       </c>
       <c r="M510" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41025,7 +41016,7 @@
         <v>87</v>
       </c>
       <c r="M511" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41055,7 +41046,7 @@
         <v>94</v>
       </c>
       <c r="M512" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41085,7 +41076,7 @@
         <v>93</v>
       </c>
       <c r="M513" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41115,7 +41106,7 @@
         <v>96</v>
       </c>
       <c r="M514" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41145,7 +41136,7 @@
         <v>89</v>
       </c>
       <c r="M515" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41175,7 +41166,7 @@
         <v>86</v>
       </c>
       <c r="M516" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41205,7 +41196,7 @@
         <v>95</v>
       </c>
       <c r="M517" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41235,7 +41226,7 @@
         <v>90</v>
       </c>
       <c r="M518" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41265,7 +41256,7 @@
         <v>90</v>
       </c>
       <c r="M519" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41295,7 +41286,7 @@
         <v>88</v>
       </c>
       <c r="M520" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41325,7 +41316,7 @@
         <v>91</v>
       </c>
       <c r="M521" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41355,7 +41346,7 @@
         <v>92</v>
       </c>
       <c r="M522" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41385,7 +41376,7 @@
         <v>92</v>
       </c>
       <c r="M523" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41415,7 +41406,7 @@
         <v>93</v>
       </c>
       <c r="M524" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41445,7 +41436,7 @@
         <v>95</v>
       </c>
       <c r="M525" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41475,7 +41466,7 @@
         <v>82</v>
       </c>
       <c r="M526" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41505,7 +41496,7 @@
         <v>89</v>
       </c>
       <c r="M527" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41535,7 +41526,7 @@
         <v>100</v>
       </c>
       <c r="M528" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41565,7 +41556,7 @@
         <v>98</v>
       </c>
       <c r="M529" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41595,7 +41586,7 @@
         <v>85</v>
       </c>
       <c r="M530" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41625,7 +41616,7 @@
         <v>87</v>
       </c>
       <c r="M531" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41655,7 +41646,7 @@
         <v>91</v>
       </c>
       <c r="M532" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41685,7 +41676,7 @@
         <v>86</v>
       </c>
       <c r="M533" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41715,7 +41706,7 @@
         <v>94</v>
       </c>
       <c r="M534" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41745,7 +41736,7 @@
         <v>100</v>
       </c>
       <c r="M535" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41775,7 +41766,7 @@
         <v>95</v>
       </c>
       <c r="M536" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41805,7 +41796,7 @@
         <v>93</v>
       </c>
       <c r="M537" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41835,7 +41826,7 @@
         <v>92</v>
       </c>
       <c r="M538" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41865,7 +41856,7 @@
         <v>93</v>
       </c>
       <c r="M539" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41895,7 +41886,7 @@
         <v>94</v>
       </c>
       <c r="M540" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41925,7 +41916,7 @@
         <v>95</v>
       </c>
       <c r="M541" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41955,7 +41946,7 @@
         <v>100</v>
       </c>
       <c r="M542" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -41985,7 +41976,7 @@
         <v>95</v>
       </c>
       <c r="M543" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42015,7 +42006,7 @@
         <v>100</v>
       </c>
       <c r="M544" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42045,7 +42036,7 @@
         <v>93</v>
       </c>
       <c r="M545" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42075,7 +42066,7 @@
         <v>91</v>
       </c>
       <c r="M546" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42105,7 +42096,7 @@
         <v>84</v>
       </c>
       <c r="M547" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42135,7 +42126,7 @@
         <v>94</v>
       </c>
       <c r="M548" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42165,7 +42156,7 @@
         <v>97</v>
       </c>
       <c r="M549" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42195,7 +42186,7 @@
         <v>99</v>
       </c>
       <c r="M550" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42225,7 +42216,7 @@
         <v>100</v>
       </c>
       <c r="M551" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42255,7 +42246,7 @@
         <v>100</v>
       </c>
       <c r="M552" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42285,7 +42276,7 @@
         <v>100</v>
       </c>
       <c r="M553" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42315,7 +42306,7 @@
         <v>95</v>
       </c>
       <c r="M554" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42345,7 +42336,7 @@
         <v>92</v>
       </c>
       <c r="M555" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42375,7 +42366,7 @@
         <v>100</v>
       </c>
       <c r="M556" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42405,7 +42396,7 @@
         <v>92</v>
       </c>
       <c r="M557" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42435,7 +42426,7 @@
         <v>100</v>
       </c>
       <c r="M558" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42465,7 +42456,7 @@
         <v>99</v>
       </c>
       <c r="M559" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42495,7 +42486,7 @@
         <v>96</v>
       </c>
       <c r="M560" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42525,7 +42516,7 @@
         <v>100</v>
       </c>
       <c r="M561" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42555,7 +42546,7 @@
         <v>99</v>
       </c>
       <c r="M562" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42585,7 +42576,7 @@
         <v>100</v>
       </c>
       <c r="M563" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42615,7 +42606,7 @@
         <v>90</v>
       </c>
       <c r="M564" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42645,7 +42636,7 @@
         <v>97</v>
       </c>
       <c r="M565" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42675,7 +42666,7 @@
         <v>100</v>
       </c>
       <c r="M566" t="str">
-        <f t="shared" ref="M566:M629" si="8">IF(F514&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M566:M629" si="10">IF(F514&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -42705,7 +42696,7 @@
         <v>100</v>
       </c>
       <c r="M567" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42735,7 +42726,7 @@
         <v>36</v>
       </c>
       <c r="M568" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42765,7 +42756,7 @@
         <v>19</v>
       </c>
       <c r="M569" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42795,7 +42786,7 @@
         <v>15</v>
       </c>
       <c r="M570" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42825,7 +42816,7 @@
         <v>22</v>
       </c>
       <c r="M571" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42855,7 +42846,7 @@
         <v>34</v>
       </c>
       <c r="M572" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42885,7 +42876,7 @@
         <v>39</v>
       </c>
       <c r="M573" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42915,7 +42906,7 @@
         <v>27</v>
       </c>
       <c r="M574" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42945,7 +42936,7 @@
         <v>36</v>
       </c>
       <c r="M575" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -42975,7 +42966,7 @@
         <v>27</v>
       </c>
       <c r="M576" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43005,7 +42996,7 @@
         <v>47</v>
       </c>
       <c r="M577" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43035,7 +43026,7 @@
         <v>45</v>
       </c>
       <c r="M578" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43065,7 +43056,7 @@
         <v>34</v>
       </c>
       <c r="M579" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43095,7 +43086,7 @@
         <v>38</v>
       </c>
       <c r="M580" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43125,7 +43116,7 @@
         <v>53</v>
       </c>
       <c r="M581" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43155,7 +43146,7 @@
         <v>50</v>
       </c>
       <c r="M582" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43185,7 +43176,7 @@
         <v>43</v>
       </c>
       <c r="M583" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43215,7 +43206,7 @@
         <v>38</v>
       </c>
       <c r="M584" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43245,7 +43236,7 @@
         <v>51</v>
       </c>
       <c r="M585" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43275,7 +43266,7 @@
         <v>34</v>
       </c>
       <c r="M586" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43305,7 +43296,7 @@
         <v>41</v>
       </c>
       <c r="M587" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43335,7 +43326,7 @@
         <v>50</v>
       </c>
       <c r="M588" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43365,7 +43356,7 @@
         <v>38</v>
       </c>
       <c r="M589" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43395,7 +43386,7 @@
         <v>53</v>
       </c>
       <c r="M590" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43425,7 +43416,7 @@
         <v>48</v>
       </c>
       <c r="M591" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43455,7 +43446,7 @@
         <v>49</v>
       </c>
       <c r="M592" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43485,7 +43476,7 @@
         <v>49</v>
       </c>
       <c r="M593" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43515,7 +43506,7 @@
         <v>37</v>
       </c>
       <c r="M594" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43545,7 +43536,7 @@
         <v>46</v>
       </c>
       <c r="M595" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43575,7 +43566,7 @@
         <v>43</v>
       </c>
       <c r="M596" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43605,7 +43596,7 @@
         <v>42</v>
       </c>
       <c r="M597" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43635,7 +43626,7 @@
         <v>36</v>
       </c>
       <c r="M598" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43665,7 +43656,7 @@
         <v>41</v>
       </c>
       <c r="M599" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43695,7 +43686,7 @@
         <v>44</v>
       </c>
       <c r="M600" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43725,7 +43716,7 @@
         <v>44</v>
       </c>
       <c r="M601" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43755,7 +43746,7 @@
         <v>49</v>
       </c>
       <c r="M602" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43785,7 +43776,7 @@
         <v>42</v>
       </c>
       <c r="M603" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43815,7 +43806,7 @@
         <v>41</v>
       </c>
       <c r="M604" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43845,7 +43836,7 @@
         <v>35</v>
       </c>
       <c r="M605" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43875,7 +43866,7 @@
         <v>41</v>
       </c>
       <c r="M606" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43905,7 +43896,7 @@
         <v>46</v>
       </c>
       <c r="M607" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43935,7 +43926,7 @@
         <v>45</v>
       </c>
       <c r="M608" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43965,7 +43956,7 @@
         <v>60</v>
       </c>
       <c r="M609" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -43995,7 +43986,7 @@
         <v>45</v>
       </c>
       <c r="M610" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44025,7 +44016,7 @@
         <v>52</v>
       </c>
       <c r="M611" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44055,7 +44046,7 @@
         <v>52</v>
       </c>
       <c r="M612" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44085,7 +44076,7 @@
         <v>41</v>
       </c>
       <c r="M613" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44115,7 +44106,7 @@
         <v>43</v>
       </c>
       <c r="M614" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44145,7 +44136,7 @@
         <v>51</v>
       </c>
       <c r="M615" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44175,7 +44166,7 @@
         <v>46</v>
       </c>
       <c r="M616" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44205,7 +44196,7 @@
         <v>51</v>
       </c>
       <c r="M617" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44235,7 +44226,7 @@
         <v>54</v>
       </c>
       <c r="M618" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44265,7 +44256,7 @@
         <v>53</v>
       </c>
       <c r="M619" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44295,7 +44286,7 @@
         <v>42</v>
       </c>
       <c r="M620" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44325,7 +44316,7 @@
         <v>48</v>
       </c>
       <c r="M621" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44355,7 +44346,7 @@
         <v>36</v>
       </c>
       <c r="M622" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44385,7 +44376,7 @@
         <v>44</v>
       </c>
       <c r="M623" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44415,7 +44406,7 @@
         <v>58</v>
       </c>
       <c r="M624" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44445,7 +44436,7 @@
         <v>53</v>
       </c>
       <c r="M625" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44475,7 +44466,7 @@
         <v>49</v>
       </c>
       <c r="M626" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44505,7 +44496,7 @@
         <v>49</v>
       </c>
       <c r="M627" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44535,7 +44526,7 @@
         <v>49</v>
       </c>
       <c r="M628" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44565,7 +44556,7 @@
         <v>50</v>
       </c>
       <c r="M629" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44595,7 +44586,7 @@
         <v>43</v>
       </c>
       <c r="M630" t="str">
-        <f t="shared" ref="M630:M693" si="9">IF(F578&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M630:M693" si="11">IF(F578&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -44625,7 +44616,7 @@
         <v>48</v>
       </c>
       <c r="M631" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44655,7 +44646,7 @@
         <v>44</v>
       </c>
       <c r="M632" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44685,7 +44676,7 @@
         <v>42</v>
       </c>
       <c r="M633" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44715,7 +44706,7 @@
         <v>40</v>
       </c>
       <c r="M634" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44745,7 +44736,7 @@
         <v>51</v>
       </c>
       <c r="M635" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44775,7 +44766,7 @@
         <v>55</v>
       </c>
       <c r="M636" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44805,7 +44796,7 @@
         <v>49</v>
       </c>
       <c r="M637" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44835,7 +44826,7 @@
         <v>37</v>
       </c>
       <c r="M638" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44865,7 +44856,7 @@
         <v>42</v>
       </c>
       <c r="M639" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44895,7 +44886,7 @@
         <v>48</v>
       </c>
       <c r="M640" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44925,7 +44916,7 @@
         <v>48</v>
       </c>
       <c r="M641" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44955,7 +44946,7 @@
         <v>40</v>
       </c>
       <c r="M642" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -44985,7 +44976,7 @@
         <v>47</v>
       </c>
       <c r="M643" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45015,7 +45006,7 @@
         <v>51</v>
       </c>
       <c r="M644" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45045,7 +45036,7 @@
         <v>45</v>
       </c>
       <c r="M645" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45075,7 +45066,7 @@
         <v>50</v>
       </c>
       <c r="M646" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45105,7 +45096,7 @@
         <v>59</v>
       </c>
       <c r="M647" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45135,7 +45126,7 @@
         <v>47</v>
       </c>
       <c r="M648" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45165,7 +45156,7 @@
         <v>52</v>
       </c>
       <c r="M649" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45195,7 +45186,7 @@
         <v>43</v>
       </c>
       <c r="M650" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45225,7 +45216,7 @@
         <v>54</v>
       </c>
       <c r="M651" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45255,7 +45246,7 @@
         <v>47</v>
       </c>
       <c r="M652" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45285,7 +45276,7 @@
         <v>54</v>
       </c>
       <c r="M653" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45315,7 +45306,7 @@
         <v>59</v>
       </c>
       <c r="M654" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45345,7 +45336,7 @@
         <v>44</v>
       </c>
       <c r="M655" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45375,7 +45366,7 @@
         <v>52</v>
       </c>
       <c r="M656" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45405,7 +45396,7 @@
         <v>44</v>
       </c>
       <c r="M657" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45435,7 +45426,7 @@
         <v>48</v>
       </c>
       <c r="M658" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45465,7 +45456,7 @@
         <v>51</v>
       </c>
       <c r="M659" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45495,7 +45486,7 @@
         <v>60</v>
       </c>
       <c r="M660" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45525,7 +45516,7 @@
         <v>52</v>
       </c>
       <c r="M661" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45555,7 +45546,7 @@
         <v>47</v>
       </c>
       <c r="M662" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45585,7 +45576,7 @@
         <v>54</v>
       </c>
       <c r="M663" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45615,7 +45606,7 @@
         <v>57</v>
       </c>
       <c r="M664" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45645,7 +45636,7 @@
         <v>51</v>
       </c>
       <c r="M665" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45675,7 +45666,7 @@
         <v>56</v>
       </c>
       <c r="M666" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45705,7 +45696,7 @@
         <v>54</v>
       </c>
       <c r="M667" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45735,7 +45726,7 @@
         <v>54</v>
       </c>
       <c r="M668" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45765,7 +45756,7 @@
         <v>54</v>
       </c>
       <c r="M669" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45795,7 +45786,7 @@
         <v>57</v>
       </c>
       <c r="M670" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45825,7 +45816,7 @@
         <v>45</v>
       </c>
       <c r="M671" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45855,7 +45846,7 @@
         <v>52</v>
       </c>
       <c r="M672" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45885,7 +45876,7 @@
         <v>48</v>
       </c>
       <c r="M673" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45915,7 +45906,7 @@
         <v>42</v>
       </c>
       <c r="M674" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45945,7 +45936,7 @@
         <v>52</v>
       </c>
       <c r="M675" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -45975,7 +45966,7 @@
         <v>54</v>
       </c>
       <c r="M676" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46005,7 +45996,7 @@
         <v>52</v>
       </c>
       <c r="M677" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46035,7 +46026,7 @@
         <v>53</v>
       </c>
       <c r="M678" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46065,7 +46056,7 @@
         <v>54</v>
       </c>
       <c r="M679" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46095,7 +46086,7 @@
         <v>58</v>
       </c>
       <c r="M680" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46125,7 +46116,7 @@
         <v>46</v>
       </c>
       <c r="M681" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46155,7 +46146,7 @@
         <v>66</v>
       </c>
       <c r="M682" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46185,7 +46176,7 @@
         <v>51</v>
       </c>
       <c r="M683" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46215,7 +46206,7 @@
         <v>47</v>
       </c>
       <c r="M684" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46245,7 +46236,7 @@
         <v>65</v>
       </c>
       <c r="M685" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46275,7 +46266,7 @@
         <v>42</v>
       </c>
       <c r="M686" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46305,7 +46296,7 @@
         <v>58</v>
       </c>
       <c r="M687" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46335,7 +46326,7 @@
         <v>52</v>
       </c>
       <c r="M688" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46365,7 +46356,7 @@
         <v>41</v>
       </c>
       <c r="M689" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46395,7 +46386,7 @@
         <v>61</v>
       </c>
       <c r="M690" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46425,7 +46416,7 @@
         <v>43</v>
       </c>
       <c r="M691" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46455,7 +46446,7 @@
         <v>47</v>
       </c>
       <c r="M692" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46485,7 +46476,7 @@
         <v>60</v>
       </c>
       <c r="M693" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46515,7 +46506,7 @@
         <v>60</v>
       </c>
       <c r="M694" t="str">
-        <f t="shared" ref="M694:M757" si="10">IF(F642&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M694:M757" si="12">IF(F642&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -46545,7 +46536,7 @@
         <v>56</v>
       </c>
       <c r="M695" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46575,7 +46566,7 @@
         <v>54</v>
       </c>
       <c r="M696" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46605,7 +46596,7 @@
         <v>51</v>
       </c>
       <c r="M697" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46635,7 +46626,7 @@
         <v>59</v>
       </c>
       <c r="M698" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46665,7 +46656,7 @@
         <v>52</v>
       </c>
       <c r="M699" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46695,7 +46686,7 @@
         <v>61</v>
       </c>
       <c r="M700" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46725,7 +46716,7 @@
         <v>56</v>
       </c>
       <c r="M701" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46755,7 +46746,7 @@
         <v>56</v>
       </c>
       <c r="M702" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46785,7 +46776,7 @@
         <v>41</v>
       </c>
       <c r="M703" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46815,7 +46806,7 @@
         <v>56</v>
       </c>
       <c r="M704" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46845,7 +46836,7 @@
         <v>62</v>
       </c>
       <c r="M705" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46875,7 +46866,7 @@
         <v>61</v>
       </c>
       <c r="M706" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46905,7 +46896,7 @@
         <v>55</v>
       </c>
       <c r="M707" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46935,7 +46926,7 @@
         <v>66</v>
       </c>
       <c r="M708" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46965,7 +46956,7 @@
         <v>55</v>
       </c>
       <c r="M709" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -46995,7 +46986,7 @@
         <v>52</v>
       </c>
       <c r="M710" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47025,7 +47016,7 @@
         <v>56</v>
       </c>
       <c r="M711" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47055,7 +47046,7 @@
         <v>46</v>
       </c>
       <c r="M712" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47085,7 +47076,7 @@
         <v>76</v>
       </c>
       <c r="M713" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47115,7 +47106,7 @@
         <v>73</v>
       </c>
       <c r="M714" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47145,7 +47136,7 @@
         <v>55</v>
       </c>
       <c r="M715" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47175,7 +47166,7 @@
         <v>69</v>
       </c>
       <c r="M716" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47205,7 +47196,7 @@
         <v>65</v>
       </c>
       <c r="M717" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47235,7 +47226,7 @@
         <v>57</v>
       </c>
       <c r="M718" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47265,7 +47256,7 @@
         <v>56</v>
       </c>
       <c r="M719" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47295,7 +47286,7 @@
         <v>54</v>
       </c>
       <c r="M720" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47325,7 +47316,7 @@
         <v>49</v>
       </c>
       <c r="M721" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47355,7 +47346,7 @@
         <v>75</v>
       </c>
       <c r="M722" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47385,7 +47376,7 @@
         <v>58</v>
       </c>
       <c r="M723" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47415,7 +47406,7 @@
         <v>55</v>
       </c>
       <c r="M724" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47445,7 +47436,7 @@
         <v>58</v>
       </c>
       <c r="M725" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47475,7 +47466,7 @@
         <v>55</v>
       </c>
       <c r="M726" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47505,7 +47496,7 @@
         <v>61</v>
       </c>
       <c r="M727" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47535,7 +47526,7 @@
         <v>68</v>
       </c>
       <c r="M728" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47565,7 +47556,7 @@
         <v>52</v>
       </c>
       <c r="M729" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47595,7 +47586,7 @@
         <v>62</v>
       </c>
       <c r="M730" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47625,7 +47616,7 @@
         <v>53</v>
       </c>
       <c r="M731" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47655,7 +47646,7 @@
         <v>58</v>
       </c>
       <c r="M732" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47685,7 +47676,7 @@
         <v>61</v>
       </c>
       <c r="M733" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47715,7 +47706,7 @@
         <v>62</v>
       </c>
       <c r="M734" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47745,7 +47736,7 @@
         <v>69</v>
       </c>
       <c r="M735" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47775,7 +47766,7 @@
         <v>67</v>
       </c>
       <c r="M736" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47805,7 +47796,7 @@
         <v>47</v>
       </c>
       <c r="M737" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47835,7 +47826,7 @@
         <v>57</v>
       </c>
       <c r="M738" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47865,7 +47856,7 @@
         <v>54</v>
       </c>
       <c r="M739" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47895,7 +47886,7 @@
         <v>66</v>
       </c>
       <c r="M740" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47925,7 +47916,7 @@
         <v>60</v>
       </c>
       <c r="M741" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47955,7 +47946,7 @@
         <v>63</v>
       </c>
       <c r="M742" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -47985,7 +47976,7 @@
         <v>56</v>
       </c>
       <c r="M743" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48015,7 +48006,7 @@
         <v>67</v>
       </c>
       <c r="M744" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48045,7 +48036,7 @@
         <v>60</v>
       </c>
       <c r="M745" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48075,7 +48066,7 @@
         <v>43</v>
       </c>
       <c r="M746" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48105,7 +48096,7 @@
         <v>58</v>
       </c>
       <c r="M747" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48135,7 +48126,7 @@
         <v>57</v>
       </c>
       <c r="M748" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48165,7 +48156,7 @@
         <v>59</v>
       </c>
       <c r="M749" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48195,7 +48186,7 @@
         <v>51</v>
       </c>
       <c r="M750" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48225,7 +48216,7 @@
         <v>67</v>
       </c>
       <c r="M751" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48255,7 +48246,7 @@
         <v>50</v>
       </c>
       <c r="M752" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48285,7 +48276,7 @@
         <v>52</v>
       </c>
       <c r="M753" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48315,7 +48306,7 @@
         <v>53</v>
       </c>
       <c r="M754" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48345,7 +48336,7 @@
         <v>57</v>
       </c>
       <c r="M755" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48375,7 +48366,7 @@
         <v>62</v>
       </c>
       <c r="M756" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48405,7 +48396,7 @@
         <v>63</v>
       </c>
       <c r="M757" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48435,7 +48426,7 @@
         <v>65</v>
       </c>
       <c r="M758" t="str">
-        <f t="shared" ref="M758:M821" si="11">IF(F706&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M758:M821" si="13">IF(F706&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -48465,7 +48456,7 @@
         <v>49</v>
       </c>
       <c r="M759" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48495,7 +48486,7 @@
         <v>68</v>
       </c>
       <c r="M760" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48525,7 +48516,7 @@
         <v>74</v>
       </c>
       <c r="M761" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48555,7 +48546,7 @@
         <v>62</v>
       </c>
       <c r="M762" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48585,7 +48576,7 @@
         <v>64</v>
       </c>
       <c r="M763" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48615,7 +48606,7 @@
         <v>70</v>
       </c>
       <c r="M764" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48645,7 +48636,7 @@
         <v>57</v>
       </c>
       <c r="M765" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48675,7 +48666,7 @@
         <v>60</v>
       </c>
       <c r="M766" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48705,7 +48696,7 @@
         <v>59</v>
       </c>
       <c r="M767" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48735,7 +48726,7 @@
         <v>52</v>
       </c>
       <c r="M768" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48765,7 +48756,7 @@
         <v>63</v>
       </c>
       <c r="M769" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48795,7 +48786,7 @@
         <v>64</v>
       </c>
       <c r="M770" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48825,7 +48816,7 @@
         <v>69</v>
       </c>
       <c r="M771" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48855,7 +48846,7 @@
         <v>64</v>
       </c>
       <c r="M772" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48885,7 +48876,7 @@
         <v>52</v>
       </c>
       <c r="M773" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48915,7 +48906,7 @@
         <v>53</v>
       </c>
       <c r="M774" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48945,7 +48936,7 @@
         <v>61</v>
       </c>
       <c r="M775" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -48975,7 +48966,7 @@
         <v>60</v>
       </c>
       <c r="M776" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49005,7 +48996,7 @@
         <v>59</v>
       </c>
       <c r="M777" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49035,7 +49026,7 @@
         <v>68</v>
       </c>
       <c r="M778" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49065,7 +49056,7 @@
         <v>70</v>
       </c>
       <c r="M779" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49095,7 +49086,7 @@
         <v>68</v>
       </c>
       <c r="M780" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49125,7 +49116,7 @@
         <v>67</v>
       </c>
       <c r="M781" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49155,7 +49146,7 @@
         <v>70</v>
       </c>
       <c r="M782" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49185,7 +49176,7 @@
         <v>63</v>
       </c>
       <c r="M783" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49215,7 +49206,7 @@
         <v>64</v>
       </c>
       <c r="M784" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49245,7 +49236,7 @@
         <v>66</v>
       </c>
       <c r="M785" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49275,7 +49266,7 @@
         <v>53</v>
       </c>
       <c r="M786" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49305,7 +49296,7 @@
         <v>53</v>
       </c>
       <c r="M787" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49335,7 +49326,7 @@
         <v>54</v>
       </c>
       <c r="M788" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49365,7 +49356,7 @@
         <v>61</v>
       </c>
       <c r="M789" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49395,7 +49386,7 @@
         <v>61</v>
       </c>
       <c r="M790" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49425,7 +49416,7 @@
         <v>74</v>
       </c>
       <c r="M791" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49455,7 +49446,7 @@
         <v>62</v>
       </c>
       <c r="M792" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49485,7 +49476,7 @@
         <v>66</v>
       </c>
       <c r="M793" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49515,7 +49506,7 @@
         <v>67</v>
       </c>
       <c r="M794" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49545,7 +49536,7 @@
         <v>59</v>
       </c>
       <c r="M795" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49575,7 +49566,7 @@
         <v>64</v>
       </c>
       <c r="M796" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49605,7 +49596,7 @@
         <v>57</v>
       </c>
       <c r="M797" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49635,7 +49626,7 @@
         <v>65</v>
       </c>
       <c r="M798" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49665,7 +49656,7 @@
         <v>69</v>
       </c>
       <c r="M799" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49695,7 +49686,7 @@
         <v>55</v>
       </c>
       <c r="M800" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49725,7 +49716,7 @@
         <v>69</v>
       </c>
       <c r="M801" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49755,7 +49746,7 @@
         <v>61</v>
       </c>
       <c r="M802" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49785,7 +49776,7 @@
         <v>53</v>
       </c>
       <c r="M803" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49815,7 +49806,7 @@
         <v>65</v>
       </c>
       <c r="M804" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49845,7 +49836,7 @@
         <v>68</v>
       </c>
       <c r="M805" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49875,7 +49866,7 @@
         <v>60</v>
       </c>
       <c r="M806" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49905,7 +49896,7 @@
         <v>57</v>
       </c>
       <c r="M807" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49935,7 +49926,7 @@
         <v>63</v>
       </c>
       <c r="M808" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49965,7 +49956,7 @@
         <v>61</v>
       </c>
       <c r="M809" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -49995,7 +49986,7 @@
         <v>71</v>
       </c>
       <c r="M810" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50025,7 +50016,7 @@
         <v>67</v>
       </c>
       <c r="M811" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50055,7 +50046,7 @@
         <v>54</v>
       </c>
       <c r="M812" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50085,7 +50076,7 @@
         <v>60</v>
       </c>
       <c r="M813" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50115,7 +50106,7 @@
         <v>76</v>
       </c>
       <c r="M814" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50145,7 +50136,7 @@
         <v>65</v>
       </c>
       <c r="M815" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50175,7 +50166,7 @@
         <v>51</v>
       </c>
       <c r="M816" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50205,7 +50196,7 @@
         <v>71</v>
       </c>
       <c r="M817" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50235,7 +50226,7 @@
         <v>74</v>
       </c>
       <c r="M818" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50265,7 +50256,7 @@
         <v>70</v>
       </c>
       <c r="M819" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50295,7 +50286,7 @@
         <v>58</v>
       </c>
       <c r="M820" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50325,7 +50316,7 @@
         <v>56</v>
       </c>
       <c r="M821" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50355,7 +50346,7 @@
         <v>72</v>
       </c>
       <c r="M822" t="str">
-        <f t="shared" ref="M822:M885" si="12">IF(F770&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M822:M885" si="14">IF(F770&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -50385,7 +50376,7 @@
         <v>70</v>
       </c>
       <c r="M823" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50415,7 +50406,7 @@
         <v>50</v>
       </c>
       <c r="M824" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50445,7 +50436,7 @@
         <v>64</v>
       </c>
       <c r="M825" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50475,7 +50466,7 @@
         <v>71</v>
       </c>
       <c r="M826" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50505,7 +50496,7 @@
         <v>65</v>
       </c>
       <c r="M827" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50535,7 +50526,7 @@
         <v>61</v>
       </c>
       <c r="M828" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50565,7 +50556,7 @@
         <v>68</v>
       </c>
       <c r="M829" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50595,7 +50586,7 @@
         <v>67</v>
       </c>
       <c r="M830" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50625,7 +50616,7 @@
         <v>69</v>
       </c>
       <c r="M831" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50655,7 +50646,7 @@
         <v>60</v>
       </c>
       <c r="M832" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50685,7 +50676,7 @@
         <v>52</v>
       </c>
       <c r="M833" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50715,7 +50706,7 @@
         <v>68</v>
       </c>
       <c r="M834" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50745,7 +50736,7 @@
         <v>68</v>
       </c>
       <c r="M835" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50775,7 +50766,7 @@
         <v>74</v>
       </c>
       <c r="M836" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50805,7 +50796,7 @@
         <v>65</v>
       </c>
       <c r="M837" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50835,7 +50826,7 @@
         <v>67</v>
       </c>
       <c r="M838" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50865,7 +50856,7 @@
         <v>68</v>
       </c>
       <c r="M839" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50895,7 +50886,7 @@
         <v>74</v>
       </c>
       <c r="M840" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50925,7 +50916,7 @@
         <v>64</v>
       </c>
       <c r="M841" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50955,7 +50946,7 @@
         <v>72</v>
       </c>
       <c r="M842" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -50985,7 +50976,7 @@
         <v>74</v>
       </c>
       <c r="M843" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51015,7 +51006,7 @@
         <v>66</v>
       </c>
       <c r="M844" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51045,7 +51036,7 @@
         <v>58</v>
       </c>
       <c r="M845" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51075,7 +51066,7 @@
         <v>63</v>
       </c>
       <c r="M846" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51105,7 +51096,7 @@
         <v>62</v>
       </c>
       <c r="M847" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51135,7 +51126,7 @@
         <v>72</v>
       </c>
       <c r="M848" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51165,7 +51156,7 @@
         <v>57</v>
       </c>
       <c r="M849" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51195,7 +51186,7 @@
         <v>68</v>
       </c>
       <c r="M850" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51225,7 +51216,7 @@
         <v>68</v>
       </c>
       <c r="M851" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51255,7 +51246,7 @@
         <v>66</v>
       </c>
       <c r="M852" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51285,7 +51276,7 @@
         <v>66</v>
       </c>
       <c r="M853" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51315,7 +51306,7 @@
         <v>63</v>
       </c>
       <c r="M854" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51345,7 +51336,7 @@
         <v>61</v>
       </c>
       <c r="M855" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51375,7 +51366,7 @@
         <v>72</v>
       </c>
       <c r="M856" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51405,7 +51396,7 @@
         <v>66</v>
       </c>
       <c r="M857" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51435,7 +51426,7 @@
         <v>75</v>
       </c>
       <c r="M858" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51465,7 +51456,7 @@
         <v>62</v>
       </c>
       <c r="M859" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51495,7 +51486,7 @@
         <v>59</v>
       </c>
       <c r="M860" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51525,7 +51516,7 @@
         <v>57</v>
       </c>
       <c r="M861" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51555,7 +51546,7 @@
         <v>57</v>
       </c>
       <c r="M862" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51585,7 +51576,7 @@
         <v>73</v>
       </c>
       <c r="M863" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51615,7 +51606,7 @@
         <v>77</v>
       </c>
       <c r="M864" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51645,7 +51636,7 @@
         <v>73</v>
       </c>
       <c r="M865" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51675,7 +51666,7 @@
         <v>76</v>
       </c>
       <c r="M866" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51705,7 +51696,7 @@
         <v>67</v>
       </c>
       <c r="M867" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51735,7 +51726,7 @@
         <v>73</v>
       </c>
       <c r="M868" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51765,7 +51756,7 @@
         <v>80</v>
       </c>
       <c r="M869" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51795,7 +51786,7 @@
         <v>75</v>
       </c>
       <c r="M870" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51825,7 +51816,7 @@
         <v>78</v>
       </c>
       <c r="M871" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51855,7 +51846,7 @@
         <v>72</v>
       </c>
       <c r="M872" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51885,7 +51876,7 @@
         <v>69</v>
       </c>
       <c r="M873" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51915,7 +51906,7 @@
         <v>60</v>
       </c>
       <c r="M874" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51945,7 +51936,7 @@
         <v>62</v>
       </c>
       <c r="M875" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -51975,7 +51966,7 @@
         <v>74</v>
       </c>
       <c r="M876" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52005,7 +51996,7 @@
         <v>65</v>
       </c>
       <c r="M877" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52035,7 +52026,7 @@
         <v>68</v>
       </c>
       <c r="M878" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52065,7 +52056,7 @@
         <v>62</v>
       </c>
       <c r="M879" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52095,7 +52086,7 @@
         <v>71</v>
       </c>
       <c r="M880" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52125,7 +52116,7 @@
         <v>69</v>
       </c>
       <c r="M881" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52155,7 +52146,7 @@
         <v>64</v>
       </c>
       <c r="M882" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52185,7 +52176,7 @@
         <v>73</v>
       </c>
       <c r="M883" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52215,7 +52206,7 @@
         <v>74</v>
       </c>
       <c r="M884" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52245,7 +52236,7 @@
         <v>60</v>
       </c>
       <c r="M885" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52275,7 +52266,7 @@
         <v>75</v>
       </c>
       <c r="M886" t="str">
-        <f t="shared" ref="M886:M949" si="13">IF(F834&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M886:M949" si="15">IF(F834&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -52305,7 +52296,7 @@
         <v>46</v>
       </c>
       <c r="M887" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52335,7 +52326,7 @@
         <v>68</v>
       </c>
       <c r="M888" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52365,7 +52356,7 @@
         <v>73</v>
       </c>
       <c r="M889" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52395,7 +52386,7 @@
         <v>79</v>
       </c>
       <c r="M890" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52425,7 +52416,7 @@
         <v>66</v>
       </c>
       <c r="M891" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52455,7 +52446,7 @@
         <v>68</v>
       </c>
       <c r="M892" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52485,7 +52476,7 @@
         <v>69</v>
       </c>
       <c r="M893" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52515,7 +52506,7 @@
         <v>73</v>
       </c>
       <c r="M894" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52545,7 +52536,7 @@
         <v>67</v>
       </c>
       <c r="M895" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52575,7 +52566,7 @@
         <v>66</v>
       </c>
       <c r="M896" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52605,7 +52596,7 @@
         <v>67</v>
       </c>
       <c r="M897" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52635,7 +52626,7 @@
         <v>72</v>
       </c>
       <c r="M898" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52665,7 +52656,7 @@
         <v>68</v>
       </c>
       <c r="M899" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52695,7 +52686,7 @@
         <v>64</v>
       </c>
       <c r="M900" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52725,7 +52716,7 @@
         <v>62</v>
       </c>
       <c r="M901" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52755,7 +52746,7 @@
         <v>64</v>
       </c>
       <c r="M902" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52785,7 +52776,7 @@
         <v>73</v>
       </c>
       <c r="M903" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52815,7 +52806,7 @@
         <v>69</v>
       </c>
       <c r="M904" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52845,7 +52836,7 @@
         <v>68</v>
       </c>
       <c r="M905" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52875,7 +52866,7 @@
         <v>77</v>
       </c>
       <c r="M906" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52905,7 +52896,7 @@
         <v>70</v>
       </c>
       <c r="M907" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52935,7 +52926,7 @@
         <v>67</v>
       </c>
       <c r="M908" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52965,7 +52956,7 @@
         <v>82</v>
       </c>
       <c r="M909" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -52995,7 +52986,7 @@
         <v>77</v>
       </c>
       <c r="M910" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53025,7 +53016,7 @@
         <v>69</v>
       </c>
       <c r="M911" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53055,7 +53046,7 @@
         <v>80</v>
       </c>
       <c r="M912" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53085,7 +53076,7 @@
         <v>86</v>
       </c>
       <c r="M913" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53115,7 +53106,7 @@
         <v>80</v>
       </c>
       <c r="M914" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53145,7 +53136,7 @@
         <v>72</v>
       </c>
       <c r="M915" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53175,7 +53166,7 @@
         <v>73</v>
       </c>
       <c r="M916" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53205,7 +53196,7 @@
         <v>82</v>
       </c>
       <c r="M917" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53235,7 +53226,7 @@
         <v>67</v>
       </c>
       <c r="M918" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53265,7 +53256,7 @@
         <v>65</v>
       </c>
       <c r="M919" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53295,7 +53286,7 @@
         <v>86</v>
       </c>
       <c r="M920" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53325,7 +53316,7 @@
         <v>78</v>
       </c>
       <c r="M921" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53355,7 +53346,7 @@
         <v>71</v>
       </c>
       <c r="M922" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53385,7 +53376,7 @@
         <v>77</v>
       </c>
       <c r="M923" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53415,7 +53406,7 @@
         <v>69</v>
       </c>
       <c r="M924" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53445,7 +53436,7 @@
         <v>65</v>
       </c>
       <c r="M925" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53475,7 +53466,7 @@
         <v>75</v>
       </c>
       <c r="M926" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53505,7 +53496,7 @@
         <v>67</v>
       </c>
       <c r="M927" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53535,7 +53526,7 @@
         <v>80</v>
       </c>
       <c r="M928" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53565,7 +53556,7 @@
         <v>72</v>
       </c>
       <c r="M929" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53595,7 +53586,7 @@
         <v>81</v>
       </c>
       <c r="M930" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53625,7 +53616,7 @@
         <v>64</v>
       </c>
       <c r="M931" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53655,7 +53646,7 @@
         <v>66</v>
       </c>
       <c r="M932" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53685,7 +53676,7 @@
         <v>79</v>
       </c>
       <c r="M933" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53715,7 +53706,7 @@
         <v>77</v>
       </c>
       <c r="M934" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53745,7 +53736,7 @@
         <v>72</v>
       </c>
       <c r="M935" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53775,7 +53766,7 @@
         <v>72</v>
       </c>
       <c r="M936" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53805,7 +53796,7 @@
         <v>63</v>
       </c>
       <c r="M937" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53835,7 +53826,7 @@
         <v>72</v>
       </c>
       <c r="M938" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53865,7 +53856,7 @@
         <v>69</v>
       </c>
       <c r="M939" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53895,7 +53886,7 @@
         <v>65</v>
       </c>
       <c r="M940" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53925,7 +53916,7 @@
         <v>81</v>
       </c>
       <c r="M941" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53955,7 +53946,7 @@
         <v>82</v>
       </c>
       <c r="M942" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -53985,7 +53976,7 @@
         <v>72</v>
       </c>
       <c r="M943" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54015,7 +54006,7 @@
         <v>64</v>
       </c>
       <c r="M944" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54045,7 +54036,7 @@
         <v>77</v>
       </c>
       <c r="M945" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54075,7 +54066,7 @@
         <v>78</v>
       </c>
       <c r="M946" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54105,7 +54096,7 @@
         <v>84</v>
       </c>
       <c r="M947" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54135,7 +54126,7 @@
         <v>73</v>
       </c>
       <c r="M948" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54165,7 +54156,7 @@
         <v>84</v>
       </c>
       <c r="M949" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54195,7 +54186,7 @@
         <v>78</v>
       </c>
       <c r="M950" t="str">
-        <f t="shared" ref="M950:M1013" si="14">IF(F898&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M950:M1013" si="16">IF(F898&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -54225,7 +54216,7 @@
         <v>79</v>
       </c>
       <c r="M951" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54255,7 +54246,7 @@
         <v>76</v>
       </c>
       <c r="M952" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54285,7 +54276,7 @@
         <v>71</v>
       </c>
       <c r="M953" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54315,7 +54306,7 @@
         <v>76</v>
       </c>
       <c r="M954" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54345,7 +54336,7 @@
         <v>74</v>
       </c>
       <c r="M955" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54375,7 +54366,7 @@
         <v>78</v>
       </c>
       <c r="M956" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54405,7 +54396,7 @@
         <v>80</v>
       </c>
       <c r="M957" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54435,7 +54426,7 @@
         <v>82</v>
       </c>
       <c r="M958" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54465,7 +54456,7 @@
         <v>77</v>
       </c>
       <c r="M959" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54495,7 +54486,7 @@
         <v>74</v>
       </c>
       <c r="M960" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54525,7 +54516,7 @@
         <v>88</v>
       </c>
       <c r="M961" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54555,7 +54546,7 @@
         <v>62</v>
       </c>
       <c r="M962" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54585,7 +54576,7 @@
         <v>61</v>
       </c>
       <c r="M963" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54615,7 +54606,7 @@
         <v>84</v>
       </c>
       <c r="M964" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54645,7 +54636,7 @@
         <v>73</v>
       </c>
       <c r="M965" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54675,7 +54666,7 @@
         <v>78</v>
       </c>
       <c r="M966" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54705,7 +54696,7 @@
         <v>73</v>
       </c>
       <c r="M967" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54735,7 +54726,7 @@
         <v>75</v>
       </c>
       <c r="M968" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54765,7 +54756,7 @@
         <v>74</v>
       </c>
       <c r="M969" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54795,7 +54786,7 @@
         <v>80</v>
       </c>
       <c r="M970" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54825,7 +54816,7 @@
         <v>81</v>
       </c>
       <c r="M971" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54855,7 +54846,7 @@
         <v>90</v>
       </c>
       <c r="M972" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54885,7 +54876,7 @@
         <v>80</v>
       </c>
       <c r="M973" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54915,7 +54906,7 @@
         <v>71</v>
       </c>
       <c r="M974" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54945,7 +54936,7 @@
         <v>78</v>
       </c>
       <c r="M975" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -54975,7 +54966,7 @@
         <v>69</v>
       </c>
       <c r="M976" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55005,7 +54996,7 @@
         <v>78</v>
       </c>
       <c r="M977" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55035,7 +55026,7 @@
         <v>71</v>
       </c>
       <c r="M978" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55065,7 +55056,7 @@
         <v>89</v>
       </c>
       <c r="M979" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55095,7 +55086,7 @@
         <v>85</v>
       </c>
       <c r="M980" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55125,7 +55116,7 @@
         <v>71</v>
       </c>
       <c r="M981" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55155,7 +55146,7 @@
         <v>68</v>
       </c>
       <c r="M982" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55185,7 +55176,7 @@
         <v>86</v>
       </c>
       <c r="M983" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55215,7 +55206,7 @@
         <v>80</v>
       </c>
       <c r="M984" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55245,7 +55236,7 @@
         <v>75</v>
       </c>
       <c r="M985" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55275,7 +55266,7 @@
         <v>70</v>
       </c>
       <c r="M986" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55305,7 +55296,7 @@
         <v>74</v>
       </c>
       <c r="M987" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55335,7 +55326,7 @@
         <v>75</v>
       </c>
       <c r="M988" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55365,7 +55356,7 @@
         <v>87</v>
       </c>
       <c r="M989" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55395,7 +55386,7 @@
         <v>73</v>
       </c>
       <c r="M990" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55425,7 +55416,7 @@
         <v>88</v>
       </c>
       <c r="M991" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55455,7 +55446,7 @@
         <v>86</v>
       </c>
       <c r="M992" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55485,7 +55476,7 @@
         <v>95</v>
       </c>
       <c r="M993" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55515,7 +55506,7 @@
         <v>72</v>
       </c>
       <c r="M994" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55545,7 +55536,7 @@
         <v>85</v>
       </c>
       <c r="M995" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55575,7 +55566,7 @@
         <v>70</v>
       </c>
       <c r="M996" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55605,7 +55596,7 @@
         <v>81</v>
       </c>
       <c r="M997" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55635,7 +55626,7 @@
         <v>76</v>
       </c>
       <c r="M998" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55665,7 +55656,7 @@
         <v>76</v>
       </c>
       <c r="M999" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55695,7 +55686,7 @@
         <v>75</v>
       </c>
       <c r="M1000" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55725,7 +55716,7 @@
         <v>76</v>
       </c>
       <c r="M1001" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55755,7 +55746,7 @@
         <v>76</v>
       </c>
       <c r="M1002" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55785,7 +55776,7 @@
         <v>86</v>
       </c>
       <c r="M1003" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55815,7 +55806,7 @@
         <v>75</v>
       </c>
       <c r="M1004" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55845,7 +55836,7 @@
         <v>78</v>
       </c>
       <c r="M1005" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55875,7 +55866,7 @@
         <v>83</v>
       </c>
       <c r="M1006" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55905,7 +55896,7 @@
         <v>75</v>
       </c>
       <c r="M1007" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55935,7 +55926,7 @@
         <v>77</v>
       </c>
       <c r="M1008" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55965,7 +55956,7 @@
         <v>82</v>
       </c>
       <c r="M1009" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -55995,7 +55986,7 @@
         <v>82</v>
       </c>
       <c r="M1010" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56025,7 +56016,7 @@
         <v>79</v>
       </c>
       <c r="M1011" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56055,7 +56046,7 @@
         <v>74</v>
       </c>
       <c r="M1012" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56085,7 +56076,7 @@
         <v>77</v>
       </c>
       <c r="M1013" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56115,7 +56106,7 @@
         <v>81</v>
       </c>
       <c r="M1014" t="str">
-        <f t="shared" ref="M1014:M1048" si="15">IF(F962&gt;=69.75,"Bonus","No Bonus")</f>
+        <f t="shared" ref="M1014:M1048" si="17">IF(F962&gt;=69.75,"Bonus","No Bonus")</f>
         <v>Bonus</v>
       </c>
     </row>
@@ -56145,7 +56136,7 @@
         <v>92</v>
       </c>
       <c r="M1015" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56175,7 +56166,7 @@
         <v>69</v>
       </c>
       <c r="M1016" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56205,7 +56196,7 @@
         <v>75</v>
       </c>
       <c r="M1017" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56235,7 +56226,7 @@
         <v>85</v>
       </c>
       <c r="M1018" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56265,7 +56256,7 @@
         <v>84</v>
       </c>
       <c r="M1019" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56295,7 +56286,7 @@
         <v>82</v>
       </c>
       <c r="M1020" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56325,7 +56316,7 @@
         <v>92</v>
       </c>
       <c r="M1021" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56355,7 +56346,7 @@
         <v>92</v>
       </c>
       <c r="M1022" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56385,7 +56376,7 @@
         <v>91</v>
       </c>
       <c r="M1023" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56415,7 +56406,7 @@
         <v>76</v>
       </c>
       <c r="M1024" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56445,7 +56436,7 @@
         <v>79</v>
       </c>
       <c r="M1025" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56475,7 +56466,7 @@
         <v>85</v>
       </c>
       <c r="M1026" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56505,7 +56496,7 @@
         <v>80</v>
       </c>
       <c r="M1027" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56535,7 +56526,7 @@
         <v>84</v>
       </c>
       <c r="M1028" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56565,7 +56556,7 @@
         <v>78</v>
       </c>
       <c r="M1029" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56595,7 +56586,7 @@
         <v>90</v>
       </c>
       <c r="M1030" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56625,7 +56616,7 @@
         <v>83</v>
       </c>
       <c r="M1031" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56655,7 +56646,7 @@
         <v>87</v>
       </c>
       <c r="M1032" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56685,7 +56676,7 @@
         <v>91</v>
       </c>
       <c r="M1033" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56715,7 +56706,7 @@
         <v>78</v>
       </c>
       <c r="M1034" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56745,7 +56736,7 @@
         <v>82</v>
       </c>
       <c r="M1035" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56775,7 +56766,7 @@
         <v>71</v>
       </c>
       <c r="M1036" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56805,7 +56796,7 @@
         <v>84</v>
       </c>
       <c r="M1037" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56835,7 +56826,7 @@
         <v>92</v>
       </c>
       <c r="M1038" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56865,7 +56856,7 @@
         <v>86</v>
       </c>
       <c r="M1039" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56895,7 +56886,7 @@
         <v>91</v>
       </c>
       <c r="M1040" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56925,7 +56916,7 @@
         <v>82</v>
       </c>
       <c r="M1041" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56955,7 +56946,7 @@
         <v>88</v>
       </c>
       <c r="M1042" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -56985,7 +56976,7 @@
         <v>90</v>
       </c>
       <c r="M1043" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -57015,7 +57006,7 @@
         <v>90</v>
       </c>
       <c r="M1044" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -57045,7 +57036,7 @@
         <v>81</v>
       </c>
       <c r="M1045" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -57075,7 +57066,7 @@
         <v>86</v>
       </c>
       <c r="M1046" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -57105,7 +57096,7 @@
         <v>99</v>
       </c>
       <c r="M1047" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -57135,7 +57126,7 @@
         <v>93</v>
       </c>
       <c r="M1048" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>Bonus</v>
       </c>
     </row>
@@ -57164,9 +57155,8 @@
       <c r="K1049" s="1">
         <v>100</v>
       </c>
-      <c r="M1049" t="e" cm="1">
-        <f t="array" ref="M1049">IF(O62SF998&gt;=69.75,"Bonus","No Bonus")</f>
-        <v>#NAME?</v>
+      <c r="M1049" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
